--- a/extenbooks/ES2305_extenbook.xlsx
+++ b/extenbooks/ES2305_extenbook.xlsx
@@ -726,7 +726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A105"/>
+  <dimension ref="A1:A139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -786,7 +786,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: study_complete</t>
         </is>
       </c>
     </row>
@@ -1325,6 +1325,232 @@
       <c r="A105" t="inlineStr">
         <is>
           <t>estimate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>## Conceptual continuity vs adjacent concepts</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>The data object `RMB misalignment estimates compiled from 4 literature</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>reviews, filtered to macroeconomic-balance methodology` measures</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>`equilibrium real-exchange-rate deviation under current-account-norm</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>calibration (Williamson 1994 family)` rather than `extended-PPP /</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>BEER` or `IMF EBA estimates` because:</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>- Source agency choice: identical to ES2304 — the same four literature</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  reviews fixed by paper note 17. No additional sources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>- Methodology continuity: the methodology filter restricts to</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  macroeconomic-balance estimates *within* the same 4 reviews; the</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  underlying calibration approach (CA-norm + RER elasticities) is</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  preserved across all sampled estimates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>- Disambiguation: macroeconomic-balance (ES2305) is methodologically</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  distinct from extended-PPP (ES2304) even when both are sampled from</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  the same 4 reviews; MB vs BEER differ in what they treat as the</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  equilibrium anchor (CA norm vs estimated fundamentals regression);</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  MB ≠ raw current-account divergence (which is the input, not the</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  output).</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>The book's original concept (Weber &amp; Shaikh 2020 Section 4.4, p. 443)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>was: even the MB approach — "directly related to the current account</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>balance and hence the methodology of choice for proponents of the</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>currency-manipulation hypothesis" — produces estimates ranging from</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>-100% to +40%, undermining the manipulation argument on its own terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>The modern series preserves the 4-review compilation rule and the</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>MB methodology filter while permitting v1.0 truncation to two</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>paper-text-named endpoints (+40% Goldstein 2004; -100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Bayoumi-Gagnon-Saborowski 2015). This is NOT a proxy substitution</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>forbidden by the No-Proxy rule because the underlying estimates are</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>verbatim from their cited working papers; the series is intrinsically</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>non-extensible past 2012 (`extension_status:</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>not_applicable_literature_compilation`).</t>
         </is>
       </c>
     </row>
@@ -1624,11 +1850,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1651,54 +1877,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>[5, 6, 7]</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>{"dpr": "Technical/docs/series/ES2305_DPR.md", "epr": "Technical/docs/series/ES2305_EPR.md", "loader": "Technical/code/L01_loaders/L01_ES2305_load.py", "processor": "Technical/code/P02_processors/P02_ES2305_construct.py", "validator": "Technical/code/V03_validators/V03_ES2305_validate.py"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>last_updated</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>author</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>opus-fanout-ES</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
